--- a/templates/今日_Cafre_Peringatan_Penipuan_B/scripts.xlsx
+++ b/templates/今日_Cafre_Peringatan_Penipuan_B/scripts.xlsx
@@ -446,34 +446,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>How to Check a Broker and Avoid Scams</t>
+          <t>Kasus BAT Bank Memanas Ini Faktanya</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Before you invest a single rupee, take sixty seconds to check your broker. It could save you from losing your money.
-Step one: verify the broker's license. Don't trust screenshots, check whether the broker is regulated by a recognized financial authority.
-Step two: search for real user reviews and complaints. If many traders report withdrawal issues or account freezes, treat it as a warning sign.
-Step three: be cautious of promises like guaranteed profits or risk-free returns. Legitimate brokers never guarantee profits.
-Step four: test the withdrawal process with a small amount before investing more.
-Step five: use trusted broker verification platforms like WikiFX to check a broker's regulation status, risk alerts, user reviews, and overall credibility, all in one place.
-A few minutes of research today can protect your savings tomorrow.
-Check first. Invest later. Stay safe from scams.</t>
+          <t>Nama Tamara alias FAS lagi ramai disorot dalam dugaan investasi BAT Instrumen Bank. Tapi, sebenarnya ada apa?
+Perlu diingat, sampai saat ini belum ada kepastian hukum mengenai peran Tamara. Namanya muncul dalam pemberitaan, tetapi itu bukan berarti otomatis bersalah.
+Yang justru perlu diwaspadai adalah modusnya. Pelaku sering memakai istilah seperti bank, instrumen bank, atau jaminan bank agar investasi terlihat resmi dan aman.
+Kalau ada yang menjanjikan keuntungan pasti, mendesak transfer cepat, atau mengaku punya akses khusus ke instrumen perbankan, itu adalah red flag.
+Sebelum mengirim uang, cek dulu legalitasnya ke OJK. Jangan mudah percaya hanya karena nama besar atau dokumen yang terlihat meyakinkan.
+Ingat, yang terdengar resmi belum tentu benar-benar resmi. Jangan sampai jadi korban berikutnya.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>how to check forex broker license regulation reviews withdrawal test WikiFX verification avoid scam</t>
+          <t>investasi bodong BAT instrumen bank Tamara OJK modus jaminan bank penipuan red flag legalitas</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>SCAM PROTECTION</t>
+          <t>PERINGATAN PENIPUAN</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>id</t>
         </is>
       </c>
     </row>
